--- a/chicago/reference/resident-research/T-0509/T-0509_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0509/T-0509_resident_research_working.xlsx
@@ -3538,7 +3538,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>L. C Chamberlain is held as a candidate and not asserted: 5 Newberry genealogical-index card(s) stand under this surname on an exact-surname rule with nothing to separate the bearers; the newberry genealogical index agreement is a surname-only refusal; the papers hold the name only on the post-office return(s) of 1834-07-16, 1835-07-01.</t>
+          <t>L. C Chamberlain is held as a candidate and not asserted: 5 Newberry genealogical-index card(s) stand under this surname on an exact-surname rule with nothing to separate the bearers; the newberry genealogical index agreement is a surname-only refusal; the papers hold the name only on the post-office return(s) of 1834-07-09 to 1834-07-16, 1835-07-01.</t>
         </is>
       </c>
     </row>
